--- a/샘플공급사/나래테크_회신.xlsx
+++ b/샘플공급사/나래테크_회신.xlsx
@@ -96,10 +96,45 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cellXfs count="2">
-    <xf numFmtId="0"/>
-    <xf numFmtId="14"/>
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Malgun Gothic"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 
